--- a/ECON251/Tutorial/T01/RAW DATA.xlsx
+++ b/ECON251/Tutorial/T01/RAW DATA.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josep\Desktop\SIM-UOW-Mods\ECON251\Tutorial\T01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99C0C62C-A505-4B0D-8C76-A2902B8689C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{945BA866-5230-4756-BD0F-3CCA752A38FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
-    <sheet name="Series - Metadata" sheetId="2" r:id="rId2"/>
+    <sheet name="SK" sheetId="3" r:id="rId2"/>
+    <sheet name="Series - Metadata" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="193">
   <si>
     <t>YR2018</t>
   </si>
@@ -4781,6 +4782,1940 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{359A453B-2AC5-4DA8-AB2B-39C77BFA37CB}">
+  <dimension ref="A1:W27"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="5" width="26.5703125" customWidth="1"/>
+    <col min="9" max="9" width="27.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:23" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G1" t="s">
+        <v>182</v>
+      </c>
+      <c r="H1" t="s">
+        <v>127</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" t="s">
+        <v>139</v>
+      </c>
+      <c r="K1" t="s">
+        <v>103</v>
+      </c>
+      <c r="L1" t="s">
+        <v>171</v>
+      </c>
+      <c r="M1" t="s">
+        <v>45</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="O1" t="s">
+        <v>82</v>
+      </c>
+      <c r="P1" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>158</v>
+      </c>
+      <c r="R1" t="s">
+        <v>185</v>
+      </c>
+      <c r="S1" t="s">
+        <v>183</v>
+      </c>
+      <c r="T1" t="s">
+        <v>93</v>
+      </c>
+      <c r="U1" t="s">
+        <v>146</v>
+      </c>
+      <c r="V1" t="s">
+        <v>172</v>
+      </c>
+      <c r="W1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C2">
+        <v>2000</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E2" s="2">
+        <v>835011437852.05408</v>
+      </c>
+      <c r="F2">
+        <v>9.2018583880478957</v>
+      </c>
+      <c r="G2">
+        <v>31.495120999046073</v>
+      </c>
+      <c r="H2">
+        <v>14.755493310487978</v>
+      </c>
+      <c r="I2" s="2">
+        <v>274764768429.46741</v>
+      </c>
+      <c r="J2">
+        <v>22567537</v>
+      </c>
+      <c r="K2">
+        <v>4.0629999999999997</v>
+      </c>
+      <c r="L2">
+        <v>26.591050957138961</v>
+      </c>
+      <c r="M2">
+        <v>15.916694563640604</v>
+      </c>
+      <c r="N2" s="2">
+        <v>200446165214.57385</v>
+      </c>
+      <c r="O2">
+        <v>3.7063477476149589</v>
+      </c>
+      <c r="P2">
+        <v>10.4366396818462</v>
+      </c>
+      <c r="Q2">
+        <v>29.0830933453176</v>
+      </c>
+      <c r="R2">
+        <v>60.480266972836098</v>
+      </c>
+      <c r="S2" t="s">
+        <v>73</v>
+      </c>
+      <c r="T2">
+        <v>3.6725092226719998E-2</v>
+      </c>
+      <c r="U2">
+        <v>54.600813990622918</v>
+      </c>
+      <c r="V2">
+        <v>10.565762255661484</v>
+      </c>
+      <c r="W2">
+        <v>1.6697877237238516</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C3">
+        <v>2001</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E3" s="2">
+        <v>874473540684.49329</v>
+      </c>
+      <c r="F3">
+        <v>4.7259356032235615</v>
+      </c>
+      <c r="G3">
+        <v>30.505835014618754</v>
+      </c>
+      <c r="H3">
+        <v>2.4876623045617663</v>
+      </c>
+      <c r="I3" s="2">
+        <v>281599987999.90369</v>
+      </c>
+      <c r="J3">
+        <v>22938753</v>
+      </c>
+      <c r="K3">
+        <v>3.6989999999999998</v>
+      </c>
+      <c r="L3">
+        <v>25.137627024451664</v>
+      </c>
+      <c r="M3">
+        <v>2.9173288572748675</v>
+      </c>
+      <c r="N3" s="2">
+        <v>206293839035.67947</v>
+      </c>
+      <c r="O3">
+        <v>3.4265877519079169</v>
+      </c>
+      <c r="P3">
+        <v>9.9046217857846308</v>
+      </c>
+      <c r="Q3">
+        <v>28.402600094385001</v>
+      </c>
+      <c r="R3">
+        <v>61.6927781198304</v>
+      </c>
+      <c r="S3" t="s">
+        <v>73</v>
+      </c>
+      <c r="T3">
+        <v>4.0290625222942002E-2</v>
+      </c>
+      <c r="U3">
+        <v>55.467242673255427</v>
+      </c>
+      <c r="V3">
+        <v>11.350536102928924</v>
+      </c>
+      <c r="W3">
+        <v>1.2980073918783235</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C4">
+        <v>2002</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" s="2">
+        <v>942192762521.07373</v>
+      </c>
+      <c r="F4">
+        <v>7.7439989531956854</v>
+      </c>
+      <c r="G4">
+        <v>30.187571612987004</v>
+      </c>
+      <c r="H4">
+        <v>7.8784587486203037</v>
+      </c>
+      <c r="I4" s="2">
+        <v>303785726890.59583</v>
+      </c>
+      <c r="J4">
+        <v>23347640</v>
+      </c>
+      <c r="K4">
+        <v>3.0459999999999998</v>
+      </c>
+      <c r="L4">
+        <v>24.77677160600247</v>
+      </c>
+      <c r="M4">
+        <v>9.2423730290835664</v>
+      </c>
+      <c r="N4" s="2">
+        <v>225360285175.37418</v>
+      </c>
+      <c r="O4">
+        <v>3.0804128842999741</v>
+      </c>
+      <c r="P4">
+        <v>9.2341353830662491</v>
+      </c>
+      <c r="Q4">
+        <v>28.266424755177901</v>
+      </c>
+      <c r="R4">
+        <v>62.499439861755903</v>
+      </c>
+      <c r="S4" t="s">
+        <v>73</v>
+      </c>
+      <c r="T4">
+        <v>3.1909859585026103E-2</v>
+      </c>
+      <c r="U4">
+        <v>56.276796076462929</v>
+      </c>
+      <c r="V4">
+        <v>11.317366624308587</v>
+      </c>
+      <c r="W4">
+        <v>1.0692853420466208</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C5">
+        <v>2003</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="2">
+        <v>971162614185.71753</v>
+      </c>
+      <c r="F5">
+        <v>3.0747266182694659</v>
+      </c>
+      <c r="G5">
+        <v>31.071962489572179</v>
+      </c>
+      <c r="H5">
+        <v>5.638610411193909</v>
+      </c>
+      <c r="I5" s="2">
+        <v>320915020514.77008</v>
+      </c>
+      <c r="J5">
+        <v>23376928</v>
+      </c>
+      <c r="K5">
+        <v>3.3479999999999999</v>
+      </c>
+      <c r="L5">
+        <v>24.431518288107529</v>
+      </c>
+      <c r="M5">
+        <v>4.7815499122946079</v>
+      </c>
+      <c r="N5" s="2">
+        <v>236135999693.52414</v>
+      </c>
+      <c r="O5">
+        <v>2.8453632521017482</v>
+      </c>
+      <c r="P5">
+        <v>8.6367424063472207</v>
+      </c>
+      <c r="Q5">
+        <v>28.540494477592802</v>
+      </c>
+      <c r="R5">
+        <v>62.822763116059903</v>
+      </c>
+      <c r="S5">
+        <v>29.522767064718298</v>
+      </c>
+      <c r="T5">
+        <v>3.4591198170787998E-2</v>
+      </c>
+      <c r="U5">
+        <v>54.450446751830924</v>
+      </c>
+      <c r="V5">
+        <v>11.692646075281191</v>
+      </c>
+      <c r="W5">
+        <v>1.4652050095920957</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C6">
+        <v>2004</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1021504157422.5989</v>
+      </c>
+      <c r="F6">
+        <v>5.1836368597333973</v>
+      </c>
+      <c r="G6">
+        <v>30.914894950637155</v>
+      </c>
+      <c r="H6">
+        <v>3.3442663882907482</v>
+      </c>
+      <c r="I6" s="2">
+        <v>331647273680.8219</v>
+      </c>
+      <c r="J6">
+        <v>23859038</v>
+      </c>
+      <c r="K6">
+        <v>3.42</v>
+      </c>
+      <c r="L6">
+        <v>26.41443238111783</v>
+      </c>
+      <c r="M6">
+        <v>10.137825034339272</v>
+      </c>
+      <c r="N6" s="2">
+        <v>260075054185.5415</v>
+      </c>
+      <c r="O6">
+        <v>2.8357744043734692</v>
+      </c>
+      <c r="P6">
+        <v>7.90037907235702</v>
+      </c>
+      <c r="Q6">
+        <v>27.935964599789202</v>
+      </c>
+      <c r="R6">
+        <v>64.163656327853701</v>
+      </c>
+      <c r="S6">
+        <v>30.523214806807399</v>
+      </c>
+      <c r="T6">
+        <v>3.1135103362705099E-2</v>
+      </c>
+      <c r="U6">
+        <v>52.052884905512897</v>
+      </c>
+      <c r="V6">
+        <v>11.885698080137637</v>
+      </c>
+      <c r="W6">
+        <v>3.2927971196496539</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C7">
+        <v>2005</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="E7" s="2">
+        <v>1066023726231.4058</v>
+      </c>
+      <c r="F7">
+        <v>4.3582366733715645</v>
+      </c>
+      <c r="G7">
+        <v>30.458567358219728</v>
+      </c>
+      <c r="H7">
+        <v>1.8749739119759283</v>
+      </c>
+      <c r="I7" s="2">
+        <v>337865573542.1167</v>
+      </c>
+      <c r="J7">
+        <v>23953153</v>
+      </c>
+      <c r="K7">
+        <v>3.4820000000000002</v>
+      </c>
+      <c r="L7">
+        <v>26.091809937041255</v>
+      </c>
+      <c r="M7">
+        <v>5.008448025253017</v>
+      </c>
+      <c r="N7" s="2">
+        <v>273100778101.07297</v>
+      </c>
+      <c r="O7">
+        <v>2.5059399070817157</v>
+      </c>
+      <c r="P7">
+        <v>7.4781133038785601</v>
+      </c>
+      <c r="Q7">
+        <v>27.422399852747901</v>
+      </c>
+      <c r="R7">
+        <v>65.099491198913299</v>
+      </c>
+      <c r="S7" t="s">
+        <v>73</v>
+      </c>
+      <c r="T7">
+        <v>3.5149387369411797E-2</v>
+      </c>
+      <c r="U7">
+        <v>52.810323405268718</v>
+      </c>
+      <c r="V7">
+        <v>12.334266669547231</v>
+      </c>
+      <c r="W7">
+        <v>2.0848784963054259</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C8">
+        <v>2006</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E8" s="2">
+        <v>1121936729365.4138</v>
+      </c>
+      <c r="F8">
+        <v>5.2450055058034195</v>
+      </c>
+      <c r="G8">
+        <v>30.50428665750119</v>
+      </c>
+      <c r="H8">
+        <v>4.1091674292794664</v>
+      </c>
+      <c r="I8" s="2">
+        <v>351749035644.8576</v>
+      </c>
+      <c r="J8">
+        <v>24205394</v>
+      </c>
+      <c r="K8">
+        <v>3.254</v>
+      </c>
+      <c r="L8">
+        <v>25.722278454477504</v>
+      </c>
+      <c r="M8">
+        <v>7.7152262581494711</v>
+      </c>
+      <c r="N8" s="2">
+        <v>294171121044.33746</v>
+      </c>
+      <c r="O8">
+        <v>2.3878051747446021</v>
+      </c>
+      <c r="P8">
+        <v>7.1832631167626202</v>
+      </c>
+      <c r="Q8">
+        <v>26.918262293156499</v>
+      </c>
+      <c r="R8">
+        <v>65.898478898771103</v>
+      </c>
+      <c r="S8">
+        <v>33.166336809862401</v>
+      </c>
+      <c r="T8">
+        <v>3.7536016435110599E-2</v>
+      </c>
+      <c r="U8">
+        <v>53.621376366692452</v>
+      </c>
+      <c r="V8">
+        <v>12.806437101353477</v>
+      </c>
+      <c r="W8">
+        <v>0.51648561410595684</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C9">
+        <v>2007</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E9" s="2">
+        <v>1187479862374.9041</v>
+      </c>
+      <c r="F9">
+        <v>5.8419633918717011</v>
+      </c>
+      <c r="G9">
+        <v>30.069121326830501</v>
+      </c>
+      <c r="H9">
+        <v>4.9899446870977044</v>
+      </c>
+      <c r="I9" s="2">
+        <v>369301117960.93561</v>
+      </c>
+      <c r="J9">
+        <v>24444660</v>
+      </c>
+      <c r="K9">
+        <v>3.0129999999999999</v>
+      </c>
+      <c r="L9">
+        <v>25.924151020328658</v>
+      </c>
+      <c r="M9">
+        <v>7.8976030798505263</v>
+      </c>
+      <c r="N9" s="2">
+        <v>317403588559.96588</v>
+      </c>
+      <c r="O9">
+        <v>2.1791273706827594</v>
+      </c>
+      <c r="P9">
+        <v>6.8841466587895503</v>
+      </c>
+      <c r="Q9">
+        <v>26.548348224117301</v>
+      </c>
+      <c r="R9">
+        <v>66.567500854891193</v>
+      </c>
+      <c r="S9">
+        <v>34.686310983059002</v>
+      </c>
+      <c r="T9">
+        <v>4.3645914016958699E-2</v>
+      </c>
+      <c r="U9">
+        <v>53.140321996211156</v>
+      </c>
+      <c r="V9">
+        <v>12.825808985534506</v>
+      </c>
+      <c r="W9">
+        <v>0.75902040763081968</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C10">
+        <v>2008</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E10" s="2">
+        <v>1223156560996.135</v>
+      </c>
+      <c r="F10">
+        <v>3.0044045167956881</v>
+      </c>
+      <c r="G10">
+        <v>30.891751593074122</v>
+      </c>
+      <c r="H10">
+        <v>-0.47484616285271386</v>
+      </c>
+      <c r="I10" s="2">
+        <v>367547505772.9259</v>
+      </c>
+      <c r="J10">
+        <v>24606329</v>
+      </c>
+      <c r="K10">
+        <v>2.9590000000000001</v>
+      </c>
+      <c r="L10">
+        <v>26.079357232403154</v>
+      </c>
+      <c r="M10">
+        <v>3.3160081120611835</v>
+      </c>
+      <c r="N10" s="2">
+        <v>327928717304.58765</v>
+      </c>
+      <c r="O10">
+        <v>2.0417916313825524</v>
+      </c>
+      <c r="P10">
+        <v>6.7204552325384803</v>
+      </c>
+      <c r="Q10">
+        <v>26.081148389690799</v>
+      </c>
+      <c r="R10">
+        <v>67.198396377770706</v>
+      </c>
+      <c r="S10">
+        <v>36.112071564681003</v>
+      </c>
+      <c r="T10">
+        <v>7.5340229239372697E-2</v>
+      </c>
+      <c r="U10">
+        <v>53.292198020420912</v>
+      </c>
+      <c r="V10">
+        <v>13.368040127919755</v>
+      </c>
+      <c r="W10">
+        <v>-0.3890528207243904</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C11">
+        <v>2009</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E11" s="2">
+        <v>1233184753860.8594</v>
+      </c>
+      <c r="F11">
+        <v>0.81986175641795001</v>
+      </c>
+      <c r="G11">
+        <v>30.887054983826644</v>
+      </c>
+      <c r="H11">
+        <v>0.85355030044634361</v>
+      </c>
+      <c r="I11" s="2">
+        <v>370684708612.7337</v>
+      </c>
+      <c r="J11">
+        <v>24664533</v>
+      </c>
+      <c r="K11">
+        <v>3.363</v>
+      </c>
+      <c r="L11">
+        <v>26.304234307903535</v>
+      </c>
+      <c r="M11">
+        <v>-1.6654234008744595</v>
+      </c>
+      <c r="N11" s="2">
+        <v>322467315708.40961</v>
+      </c>
+      <c r="O11">
+        <v>2.1380452806109744</v>
+      </c>
+      <c r="P11">
+        <v>6.5901698708343197</v>
+      </c>
+      <c r="Q11">
+        <v>25.2405293646679</v>
+      </c>
+      <c r="R11">
+        <v>68.169313548243196</v>
+      </c>
+      <c r="S11" t="s">
+        <v>73</v>
+      </c>
+      <c r="T11">
+        <v>5.79313041903032E-2</v>
+      </c>
+      <c r="U11">
+        <v>52.541703991578146</v>
+      </c>
+      <c r="V11">
+        <v>13.955320039623819</v>
+      </c>
+      <c r="W11">
+        <v>3.8966291472474235</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>62</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C12">
+        <v>2010</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E12" s="2">
+        <v>1319281537670.4104</v>
+      </c>
+      <c r="F12">
+        <v>6.9816613885307106</v>
+      </c>
+      <c r="G12">
+        <v>30.46279986910822</v>
+      </c>
+      <c r="H12">
+        <v>6.6602462488005756</v>
+      </c>
+      <c r="I12" s="2">
+        <v>395373223012.9906</v>
+      </c>
+      <c r="J12">
+        <v>24998081</v>
+      </c>
+      <c r="K12">
+        <v>3.3239999999999998</v>
+      </c>
+      <c r="L12">
+        <v>28.099005683527512</v>
+      </c>
+      <c r="M12">
+        <v>14.0267947435389</v>
+      </c>
+      <c r="N12" s="2">
+        <v>367699144197.82776</v>
+      </c>
+      <c r="O12">
+        <v>2.0444228836758027</v>
+      </c>
+      <c r="P12">
+        <v>6.19072327209956</v>
+      </c>
+      <c r="Q12">
+        <v>25.7541683041255</v>
+      </c>
+      <c r="R12">
+        <v>68.055095810419203</v>
+      </c>
+      <c r="S12" t="s">
+        <v>73</v>
+      </c>
+      <c r="T12">
+        <v>7.4640030674355901E-2</v>
+      </c>
+      <c r="U12">
+        <v>51.200788540329036</v>
+      </c>
+      <c r="V12">
+        <v>13.504108346148733</v>
+      </c>
+      <c r="W12">
+        <v>2.5158536650785579</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>62</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C13">
+        <v>2011</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E13" s="2">
+        <v>1367937063745.2507</v>
+      </c>
+      <c r="F13">
+        <v>3.6880320602951997</v>
+      </c>
+      <c r="G13">
+        <v>30.579957304264958</v>
+      </c>
+      <c r="H13">
+        <v>1.9338343362178563</v>
+      </c>
+      <c r="I13" s="2">
+        <v>403019086155.82703</v>
+      </c>
+      <c r="J13">
+        <v>25497708</v>
+      </c>
+      <c r="K13">
+        <v>2.992</v>
+      </c>
+      <c r="L13">
+        <v>29.000557513187434</v>
+      </c>
+      <c r="M13">
+        <v>5.1510134312347873</v>
+      </c>
+      <c r="N13" s="2">
+        <v>386639376501.99323</v>
+      </c>
+      <c r="O13">
+        <v>2.1076566525074703</v>
+      </c>
+      <c r="P13">
+        <v>5.9598917005725598</v>
+      </c>
+      <c r="Q13">
+        <v>25.607232279291701</v>
+      </c>
+      <c r="R13">
+        <v>68.432876020135794</v>
+      </c>
+      <c r="S13">
+        <v>39.3404518967575</v>
+      </c>
+      <c r="T13">
+        <v>9.1417598873579406E-2</v>
+      </c>
+      <c r="U13">
+        <v>52.148199928260567</v>
+      </c>
+      <c r="V13">
+        <v>13.708431924436667</v>
+      </c>
+      <c r="W13">
+        <v>0.88202507345836834</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>62</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C14">
+        <v>2012</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E14" s="2">
+        <v>1402787524457.7334</v>
+      </c>
+      <c r="F14">
+        <v>2.5476655056824171</v>
+      </c>
+      <c r="G14">
+        <v>29.855428494449399</v>
+      </c>
+      <c r="H14">
+        <v>-0.25125161085924219</v>
+      </c>
+      <c r="I14" s="2">
+        <v>402006494209.79034</v>
+      </c>
+      <c r="J14">
+        <v>25940388</v>
+      </c>
+      <c r="K14">
+        <v>2.8119999999999998</v>
+      </c>
+      <c r="L14">
+        <v>28.740868205281128</v>
+      </c>
+      <c r="M14">
+        <v>1.7496539392847694</v>
+      </c>
+      <c r="N14" s="2">
+        <v>393404227583.78644</v>
+      </c>
+      <c r="O14">
+        <v>2.0821518759444322</v>
+      </c>
+      <c r="P14">
+        <v>5.7508481535728402</v>
+      </c>
+      <c r="Q14">
+        <v>25.364701620319799</v>
+      </c>
+      <c r="R14">
+        <v>68.884442197011197</v>
+      </c>
+      <c r="S14">
+        <v>40.292341943066603</v>
+      </c>
+      <c r="T14">
+        <v>0.10081809751226201</v>
+      </c>
+      <c r="U14">
+        <v>52.252617360795938</v>
+      </c>
+      <c r="V14">
+        <v>14.00263352708736</v>
+      </c>
+      <c r="W14">
+        <v>2.5297903379874755</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>62</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C15">
+        <v>2013</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E15" s="2">
+        <v>1448958816285.7803</v>
+      </c>
+      <c r="F15">
+        <v>3.2913959543441962</v>
+      </c>
+      <c r="G15">
+        <v>29.234861053095536</v>
+      </c>
+      <c r="H15">
+        <v>2.4451936046663576</v>
+      </c>
+      <c r="I15" s="2">
+        <v>411836331296.55157</v>
+      </c>
+      <c r="J15">
+        <v>26423747</v>
+      </c>
+      <c r="K15">
+        <v>3.0670000000000002</v>
+      </c>
+      <c r="L15">
+        <v>28.865476694118204</v>
+      </c>
+      <c r="M15">
+        <v>3.5019398864828588</v>
+      </c>
+      <c r="N15" s="2">
+        <v>407181007144.65289</v>
+      </c>
+      <c r="O15">
+        <v>1.9950816652112731</v>
+      </c>
+      <c r="P15">
+        <v>5.6031180822298499</v>
+      </c>
+      <c r="Q15">
+        <v>25.5708663166637</v>
+      </c>
+      <c r="R15">
+        <v>68.826007736932098</v>
+      </c>
+      <c r="S15">
+        <v>41.320164425194797</v>
+      </c>
+      <c r="T15">
+        <v>7.2371715347611401E-2</v>
+      </c>
+      <c r="U15">
+        <v>51.541085448173583</v>
+      </c>
+      <c r="V15">
+        <v>14.259701622890066</v>
+      </c>
+      <c r="W15">
+        <v>4.3001946225510332</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>62</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C16">
+        <v>2014</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E16" s="2">
+        <v>1495538208413.1575</v>
+      </c>
+      <c r="F16">
+        <v>3.2146801968310825</v>
+      </c>
+      <c r="G16">
+        <v>29.192580852748833</v>
+      </c>
+      <c r="H16">
+        <v>3.5986349780257001</v>
+      </c>
+      <c r="I16" s="2">
+        <v>426656817566.80713</v>
+      </c>
+      <c r="J16">
+        <v>27115956</v>
+      </c>
+      <c r="K16">
+        <v>3.0819999999999999</v>
+      </c>
+      <c r="L16">
+        <v>28.276075554683207</v>
+      </c>
+      <c r="M16">
+        <v>3.3452618232818594</v>
+      </c>
+      <c r="N16" s="2">
+        <v>420802277928.3175</v>
+      </c>
+      <c r="O16">
+        <v>1.9517666566085934</v>
+      </c>
+      <c r="P16">
+        <v>5.22810861880708</v>
+      </c>
+      <c r="Q16">
+        <v>25.759622749095801</v>
+      </c>
+      <c r="R16">
+        <v>69.012272452839198</v>
+      </c>
+      <c r="S16">
+        <v>42.319487584761802</v>
+      </c>
+      <c r="T16">
+        <v>6.40735784174601E-2</v>
+      </c>
+      <c r="U16">
+        <v>51.082591672501323</v>
+      </c>
+      <c r="V16">
+        <v>14.487030944687431</v>
+      </c>
+      <c r="W16">
+        <v>4.6409829374065596</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>62</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C17">
+        <v>2015</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" s="2">
+        <v>1539212301135.5471</v>
+      </c>
+      <c r="F17">
+        <v>2.9202926730123409</v>
+      </c>
+      <c r="G17">
+        <v>29.180084054467663</v>
+      </c>
+      <c r="H17">
+        <v>5.2704245556161737</v>
+      </c>
+      <c r="I17" s="2">
+        <v>449143443248.05859</v>
+      </c>
+      <c r="J17">
+        <v>27531028</v>
+      </c>
+      <c r="K17">
+        <v>3.5459999999999998</v>
+      </c>
+      <c r="L17">
+        <v>27.821592209451417</v>
+      </c>
+      <c r="M17">
+        <v>1.7659342929207327</v>
+      </c>
+      <c r="N17" s="2">
+        <v>428233369659.64526</v>
+      </c>
+      <c r="O17">
+        <v>1.8985843095263262</v>
+      </c>
+      <c r="P17">
+        <v>5.1089099748080304</v>
+      </c>
+      <c r="Q17">
+        <v>25.425734333697001</v>
+      </c>
+      <c r="R17">
+        <v>69.465359459588996</v>
+      </c>
+      <c r="S17" t="s">
+        <v>73</v>
+      </c>
+      <c r="T17">
+        <v>3.6748014230867099E-2</v>
+      </c>
+      <c r="U17">
+        <v>49.793241634765181</v>
+      </c>
+      <c r="V17">
+        <v>14.346463875880641</v>
+      </c>
+      <c r="W17">
+        <v>6.5480854515457469</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>62</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C18">
+        <v>2016</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18" s="2">
+        <v>1588028842393.0498</v>
+      </c>
+      <c r="F18">
+        <v>3.1715274898393488</v>
+      </c>
+      <c r="G18">
+        <v>29.866216889596693</v>
+      </c>
+      <c r="H18">
+        <v>6.8356634925446542</v>
+      </c>
+      <c r="I18" s="2">
+        <v>479845377627.32416</v>
+      </c>
+      <c r="J18">
+        <v>27791833</v>
+      </c>
+      <c r="K18">
+        <v>3.65</v>
+      </c>
+      <c r="L18">
+        <v>27.512994083119143</v>
+      </c>
+      <c r="M18">
+        <v>2.0742825624471237</v>
+      </c>
+      <c r="N18" s="2">
+        <v>437116139773.07501</v>
+      </c>
+      <c r="O18">
+        <v>1.739456481428038</v>
+      </c>
+      <c r="P18">
+        <v>4.8184066200092603</v>
+      </c>
+      <c r="Q18">
+        <v>25.220937987768998</v>
+      </c>
+      <c r="R18">
+        <v>69.960655392221796</v>
+      </c>
+      <c r="S18">
+        <v>43.687993673726801</v>
+      </c>
+      <c r="T18">
+        <v>3.3110193136481898E-2</v>
+      </c>
+      <c r="U18">
+        <v>49.249825398060239</v>
+      </c>
+      <c r="V18">
+        <v>14.441530744834798</v>
+      </c>
+      <c r="W18">
+        <v>6.326252985090342</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>62</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C19">
+        <v>2017</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" s="2">
+        <v>1642548917819.5881</v>
+      </c>
+      <c r="F19">
+        <v>3.4331917639720047</v>
+      </c>
+      <c r="G19">
+        <v>31.698513814694284</v>
+      </c>
+      <c r="H19">
+        <v>9.9455306985263263</v>
+      </c>
+      <c r="I19" s="2">
+        <v>527568546964.70929</v>
+      </c>
+      <c r="J19">
+        <v>28106147</v>
+      </c>
+      <c r="K19">
+        <v>3.653</v>
+      </c>
+      <c r="L19">
+        <v>28.0322405682167</v>
+      </c>
+      <c r="M19">
+        <v>4.2550032245209763</v>
+      </c>
+      <c r="N19" s="2">
+        <v>455715445615.32092</v>
+      </c>
+      <c r="O19">
+        <v>1.7149425413338069</v>
+      </c>
+      <c r="P19">
+        <v>4.78443073470189</v>
+      </c>
+      <c r="Q19">
+        <v>25.308127526024599</v>
+      </c>
+      <c r="R19">
+        <v>69.907452790962097</v>
+      </c>
+      <c r="S19">
+        <v>44.381579110173398</v>
+      </c>
+      <c r="T19">
+        <v>3.8602274168195699E-2</v>
+      </c>
+      <c r="U19">
+        <v>48.954860112833302</v>
+      </c>
+      <c r="V19">
+        <v>14.574209458328696</v>
+      </c>
+      <c r="W19">
+        <v>4.5056391577047634</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>62</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C20">
+        <v>2018</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E20" s="2">
+        <v>1694718171579.2532</v>
+      </c>
+      <c r="F20">
+        <v>3.1761156817732683</v>
+      </c>
+      <c r="G20">
+        <v>30.494986358820203</v>
+      </c>
+      <c r="H20">
+        <v>-1.9983530735552648</v>
+      </c>
+      <c r="I20" s="2">
+        <v>517025864691.32922</v>
+      </c>
+      <c r="J20">
+        <v>28257879</v>
+      </c>
+      <c r="K20">
+        <v>3.8239999999999998</v>
+      </c>
+      <c r="L20">
+        <v>27.767223748981362</v>
+      </c>
+      <c r="M20">
+        <v>3.3886786526351642</v>
+      </c>
+      <c r="N20" s="2">
+        <v>471158177637.64856</v>
+      </c>
+      <c r="O20">
+        <v>1.5993277443236076</v>
+      </c>
+      <c r="P20">
+        <v>4.9965217980675698</v>
+      </c>
+      <c r="Q20">
+        <v>25.202011748184798</v>
+      </c>
+      <c r="R20">
+        <v>69.801462778166993</v>
+      </c>
+      <c r="S20">
+        <v>45.311374208937302</v>
+      </c>
+      <c r="T20">
+        <v>4.7121517152711401E-2</v>
+      </c>
+      <c r="U20">
+        <v>49.413896389814624</v>
+      </c>
+      <c r="V20">
+        <v>15.140262120918827</v>
+      </c>
+      <c r="W20">
+        <v>4.1971833722849992</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>62</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C21">
+        <v>2019</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E21" s="2">
+        <v>1733930596323.252</v>
+      </c>
+      <c r="F21">
+        <v>2.3138021059547498</v>
+      </c>
+      <c r="G21">
+        <v>30.112526532099004</v>
+      </c>
+      <c r="H21">
+        <v>-2.0890757941034792</v>
+      </c>
+      <c r="I21" s="2">
+        <v>506224802502.80847</v>
+      </c>
+      <c r="J21">
+        <v>28561856</v>
+      </c>
+      <c r="K21">
+        <v>3.746</v>
+      </c>
+      <c r="L21">
+        <v>26.370175590513018</v>
+      </c>
+      <c r="M21">
+        <v>0.495587240722827</v>
+      </c>
+      <c r="N21" s="2">
+        <v>473493177449.64294</v>
+      </c>
+      <c r="O21">
+        <v>1.5068943395558834</v>
+      </c>
+      <c r="P21">
+        <v>5.1429876456285299</v>
+      </c>
+      <c r="Q21">
+        <v>24.578098325109</v>
+      </c>
+      <c r="R21">
+        <v>70.278917666463499</v>
+      </c>
+      <c r="S21">
+        <v>46.005800472779399</v>
+      </c>
+      <c r="T21">
+        <v>0.12145300522038099</v>
+      </c>
+      <c r="U21">
+        <v>50.105829463504826</v>
+      </c>
+      <c r="V21">
+        <v>16.062987140559983</v>
+      </c>
+      <c r="W21">
+        <v>2.6355900337465417</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>62</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C22">
+        <v>2020</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" s="2">
+        <v>1721788880530.9863</v>
+      </c>
+      <c r="F22">
+        <v>-0.70024231754210575</v>
+      </c>
+      <c r="G22">
+        <v>31.040908365523556</v>
+      </c>
+      <c r="H22">
+        <v>2.7835195490286964</v>
+      </c>
+      <c r="I22" s="2">
+        <v>520315668842.50604</v>
+      </c>
+      <c r="J22">
+        <v>28369827</v>
+      </c>
+      <c r="K22">
+        <v>3.931</v>
+      </c>
+      <c r="L22">
+        <v>25.700243360773662</v>
+      </c>
+      <c r="M22">
+        <v>-2.0028411958956269</v>
+      </c>
+      <c r="N22" s="2">
+        <v>464009861031.92633</v>
+      </c>
+      <c r="O22">
+        <v>1.5779513535925895</v>
+      </c>
+      <c r="P22">
+        <v>5.3712067844012097</v>
+      </c>
+      <c r="Q22">
+        <v>24.6462264496937</v>
+      </c>
+      <c r="R22">
+        <v>69.982566765905105</v>
+      </c>
+      <c r="S22">
+        <v>46.453575045308902</v>
+      </c>
+      <c r="T22">
+        <v>0.113270922936166</v>
+      </c>
+      <c r="U22">
+        <v>47.80685039081277</v>
+      </c>
+      <c r="V22">
+        <v>16.982846211002219</v>
+      </c>
+      <c r="W22">
+        <v>3.6854425369565158</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>62</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C23">
+        <v>2021</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="E23" s="2">
+        <v>1801214449834.7632</v>
+      </c>
+      <c r="F23">
+        <v>4.6129679545428672</v>
+      </c>
+      <c r="G23">
+        <v>31.487764439371141</v>
+      </c>
+      <c r="H23">
+        <v>4.3170950849238352</v>
+      </c>
+      <c r="I23" s="2">
+        <v>542778191008.19446</v>
+      </c>
+      <c r="J23">
+        <v>28560792</v>
+      </c>
+      <c r="K23">
+        <v>3.6389999999999998</v>
+      </c>
+      <c r="L23">
+        <v>26.248085602275406</v>
+      </c>
+      <c r="M23">
+        <v>6.4767294311164108</v>
+      </c>
+      <c r="N23" s="2">
+        <v>494062524264.66345</v>
+      </c>
+      <c r="O23">
+        <v>1.6651597819158437</v>
+      </c>
+      <c r="P23">
+        <v>5.3469953349631396</v>
+      </c>
+      <c r="Q23">
+        <v>24.6038800147514</v>
+      </c>
+      <c r="R23">
+        <v>70.049124650285506</v>
+      </c>
+      <c r="S23">
+        <v>46.9363236351046</v>
+      </c>
+      <c r="T23">
+        <v>4.9812574781782998E-2</v>
+      </c>
+      <c r="U23">
+        <v>47.111306658330307</v>
+      </c>
+      <c r="V23">
+        <v>17.024438716747177</v>
+      </c>
+      <c r="W23">
+        <v>3.3713337728045056</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>62</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C24">
+        <v>2022</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="E24" s="2">
+        <v>1850343736945.7598</v>
+      </c>
+      <c r="F24">
+        <v>2.7275645670899138</v>
+      </c>
+      <c r="G24">
+        <v>31.933893096231291</v>
+      </c>
+      <c r="H24">
+        <v>-0.17018940021888795</v>
+      </c>
+      <c r="I24" s="2">
+        <v>541854440060.39868</v>
+      </c>
+      <c r="J24">
+        <v>29201402</v>
+      </c>
+      <c r="K24">
+        <v>2.8570000000000002</v>
+      </c>
+      <c r="L24">
+        <v>26.497740859026546</v>
+      </c>
+      <c r="M24">
+        <v>2.4734828015454724</v>
+      </c>
+      <c r="N24" s="2">
+        <v>506283075831.23132</v>
+      </c>
+      <c r="O24">
+        <v>1.4483461547481982</v>
+      </c>
+      <c r="P24">
+        <v>5.4318017027852203</v>
+      </c>
+      <c r="Q24">
+        <v>24.4572753776052</v>
+      </c>
+      <c r="R24">
+        <v>70.110926437353797</v>
+      </c>
+      <c r="S24">
+        <v>47.509916716251396</v>
+      </c>
+      <c r="T24" t="s">
+        <v>73</v>
+      </c>
+      <c r="U24">
+        <v>49.03202818337266</v>
+      </c>
+      <c r="V24">
+        <v>17.637910448981543</v>
+      </c>
+      <c r="W24">
+        <v>4.5744404110283172E-3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>62</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C25">
+        <v>2023</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E25" s="2">
+        <v>1879634949821.7227</v>
+      </c>
+      <c r="F25">
+        <v>1.583014674036292</v>
+      </c>
+      <c r="G25">
+        <v>31.447015498980896</v>
+      </c>
+      <c r="H25">
+        <v>-0.23672370307285462</v>
+      </c>
+      <c r="I25" s="2">
+        <v>540571742164.62305</v>
+      </c>
+      <c r="J25">
+        <v>29587631</v>
+      </c>
+      <c r="K25">
+        <v>2.6749999999999998</v>
+      </c>
+      <c r="L25">
+        <v>25.45514208277919</v>
+      </c>
+      <c r="M25">
+        <v>1.4764188419199513</v>
+      </c>
+      <c r="N25" s="2">
+        <v>513757934556.25555</v>
+      </c>
+      <c r="O25">
+        <v>1.447738714455018</v>
+      </c>
+      <c r="P25">
+        <v>5.3243284220251796</v>
+      </c>
+      <c r="Q25">
+        <v>23.991423224180199</v>
+      </c>
+      <c r="R25">
+        <v>70.684251824038</v>
+      </c>
+      <c r="S25">
+        <v>48.651511322086101</v>
+      </c>
+      <c r="T25" t="s">
+        <v>73</v>
+      </c>
+      <c r="U25">
+        <v>49.948644228387629</v>
+      </c>
+      <c r="V25">
+        <v>17.775183280321059</v>
+      </c>
+      <c r="W25">
+        <v>0.38495240187664037</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>62</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C26">
+        <v>2024</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E26" s="2">
+        <v>1917295522781.8574</v>
+      </c>
+      <c r="F26">
+        <v>2.0036110183898614</v>
+      </c>
+      <c r="G26">
+        <v>30.029371211706994</v>
+      </c>
+      <c r="H26">
+        <v>-0.77010806338076065</v>
+      </c>
+      <c r="I26" s="2">
+        <v>536408755589.85547</v>
+      </c>
+      <c r="J26">
+        <v>29835657</v>
+      </c>
+      <c r="K26">
+        <v>2.7839999999999998</v>
+      </c>
+      <c r="L26">
+        <v>26.617972515792239</v>
+      </c>
+      <c r="M26">
+        <v>4.2979762188687545</v>
+      </c>
+      <c r="N26" s="2">
+        <v>535839128406.03473</v>
+      </c>
+      <c r="O26">
+        <v>1.4582510545953795</v>
+      </c>
+      <c r="P26">
+        <v>5.19680870662354</v>
+      </c>
+      <c r="Q26">
+        <v>23.6590890618115</v>
+      </c>
+      <c r="R26">
+        <v>71.144105681492505</v>
+      </c>
+      <c r="S26">
+        <v>49.555738683101303</v>
+      </c>
+      <c r="T26" t="s">
+        <v>73</v>
+      </c>
+      <c r="U26">
+        <v>48.486294151562774</v>
+      </c>
+      <c r="V26">
+        <v>17.484608253866639</v>
+      </c>
+      <c r="W26">
+        <v>4.0739815994431288</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>62</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C27">
+        <v>2025</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E27" s="2">
+        <v>1936603041534.4866</v>
+      </c>
+      <c r="F27">
+        <v>1.0070184029124221</v>
+      </c>
+      <c r="G27">
+        <v>28.329933970943127</v>
+      </c>
+      <c r="H27">
+        <v>-3.2262099653636369</v>
+      </c>
+      <c r="I27" s="2">
+        <v>519103082861.9325</v>
+      </c>
+      <c r="J27">
+        <v>29865575</v>
+      </c>
+      <c r="K27">
+        <v>2.6829999999999998</v>
+      </c>
+      <c r="L27">
+        <v>27.426332609255756</v>
+      </c>
+      <c r="M27">
+        <v>2.0257298148464997</v>
+      </c>
+      <c r="N27" s="2">
+        <v>546693781389.76941</v>
+      </c>
+      <c r="O27">
+        <v>1.464272752592926</v>
+      </c>
+      <c r="P27">
+        <v>5.1038276892102497</v>
+      </c>
+      <c r="Q27">
+        <v>23.382817244350701</v>
+      </c>
+      <c r="R27">
+        <v>71.513365391935906</v>
+      </c>
+      <c r="S27" t="s">
+        <v>73</v>
+      </c>
+      <c r="T27" t="s">
+        <v>73</v>
+      </c>
+      <c r="U27">
+        <v>48.021963077525214</v>
+      </c>
+      <c r="V27">
+        <v>17.647665756557192</v>
+      </c>
+      <c r="W27">
+        <v>5.1644763989431928</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:W27">
+    <sortCondition ref="C2:C27"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:P20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
